--- a/backend/Dataset/streaks.xlsx
+++ b/backend/Dataset/streaks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofexeteruk-my.sharepoint.com/personal/whm208_exeter_ac_uk/Documents/Year 2/COM2020/Coursework 1/Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="340" documentId="11_F25DC773A252ABDACC104804C11A51C05ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B80DBF4-DD2D-40FB-AD6A-72FB99E37770}"/>
+  <xr:revisionPtr revIDLastSave="429" documentId="11_F25DC773A252ABDACC104804C11A51C05ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22217A9C-06D9-4946-893C-BB62631266B0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="9">
   <si>
     <t>streakID</t>
   </si>
@@ -50,13 +50,16 @@
   <si>
     <t>NULL</t>
   </si>
+  <si>
+    <t>currentWeekStart</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ hh:mm"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -110,11 +113,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -399,15 +403,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.5703125" customWidth="1"/>
     <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" customWidth="1"/>
+    <col min="6" max="6" width="30.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -423,8 +429,11 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -434,14 +443,17 @@
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3">
-        <v>45536</v>
-      </c>
-      <c r="E2" s="3">
-        <v>45550</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D2" s="4">
+        <v>45536.729166666664</v>
+      </c>
+      <c r="E2" s="4">
+        <v>45550.729166666664</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -451,14 +463,17 @@
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="3">
-        <v>45546</v>
-      </c>
-      <c r="E3" s="3">
-        <v>45555</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D3" s="4">
+        <v>45546.729166666664</v>
+      </c>
+      <c r="E3" s="4">
+        <v>45555.729166666664</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -468,14 +483,17 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="3">
-        <v>45556</v>
-      </c>
-      <c r="E4" s="3">
-        <v>45590</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D4" s="4">
+        <v>45556.729166666664</v>
+      </c>
+      <c r="E4" s="4">
+        <v>45590.729166666664</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -485,14 +503,17 @@
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3">
-        <v>45569</v>
-      </c>
-      <c r="E5" s="3">
-        <v>45695</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D5" s="4">
+        <v>45569.729166666664</v>
+      </c>
+      <c r="E5" s="4">
+        <v>45695.729166666664</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -502,14 +523,17 @@
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="3">
-        <v>45597</v>
-      </c>
-      <c r="E6" s="3">
-        <v>45632</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D6" s="4">
+        <v>45597.729166666664</v>
+      </c>
+      <c r="E6" s="4">
+        <v>45632.729166666664</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -519,14 +543,17 @@
       <c r="C7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="3">
-        <v>45647</v>
-      </c>
-      <c r="E7" s="3">
-        <v>46011</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D7" s="4">
+        <v>45647.729166666664</v>
+      </c>
+      <c r="E7" s="4">
+        <v>46011.729166666664</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -536,14 +563,17 @@
       <c r="C8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="3">
-        <v>45659</v>
-      </c>
-      <c r="E8" s="3">
-        <v>45729</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D8" s="4">
+        <v>45659.729166666664</v>
+      </c>
+      <c r="E8" s="4">
+        <v>45729.729166666664</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -553,14 +583,17 @@
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
-        <v>45702</v>
-      </c>
-      <c r="E9" s="3">
-        <v>45716</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D9" s="4">
+        <v>45702.729166666664</v>
+      </c>
+      <c r="E9" s="4">
+        <v>45716.729166666664</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -570,14 +603,17 @@
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>45717</v>
-      </c>
-      <c r="E10" s="3">
-        <v>45745</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D10" s="4">
+        <v>45717.729166666664</v>
+      </c>
+      <c r="E10" s="4">
+        <v>45745.729166666664</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -587,14 +623,17 @@
       <c r="C11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="3">
-        <v>45737</v>
-      </c>
-      <c r="E11" s="3">
-        <v>45772</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D11" s="4">
+        <v>45737.729166666664</v>
+      </c>
+      <c r="E11" s="4">
+        <v>45772.729166666664</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -604,14 +643,17 @@
       <c r="C12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="3">
-        <v>45748</v>
-      </c>
-      <c r="E12" s="3">
-        <v>45769</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D12" s="4">
+        <v>45748.729166666664</v>
+      </c>
+      <c r="E12" s="4">
+        <v>45769.729166666664</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -621,14 +663,17 @@
       <c r="C13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="3">
-        <v>45781</v>
-      </c>
-      <c r="E13" s="3">
-        <v>45802</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D13" s="4">
+        <v>45781.729166666664</v>
+      </c>
+      <c r="E13" s="4">
+        <v>45802.729166666664</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -638,14 +683,17 @@
       <c r="C14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="3">
-        <v>45803</v>
-      </c>
-      <c r="E14" s="3">
-        <v>45817</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D14" s="4">
+        <v>45803.729166666664</v>
+      </c>
+      <c r="E14" s="4">
+        <v>45817.729166666664</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -655,14 +703,17 @@
       <c r="C15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="3">
-        <v>45829</v>
-      </c>
-      <c r="E15" s="3">
-        <v>45843</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D15" s="4">
+        <v>45829.729166666664</v>
+      </c>
+      <c r="E15" s="4">
+        <v>45843.729166666664</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -672,14 +723,17 @@
       <c r="C16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="3">
-        <v>45901</v>
-      </c>
-      <c r="E16" s="3">
-        <v>45936</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D16" s="4">
+        <v>45901.729166666664</v>
+      </c>
+      <c r="E16" s="4">
+        <v>45936.729166666664</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -689,14 +743,17 @@
       <c r="C17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="3">
-        <v>45961</v>
+      <c r="D17" s="4">
+        <v>45961.729166666664</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" s="4">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -706,14 +763,17 @@
       <c r="C18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="3">
-        <v>45977</v>
+      <c r="D18" s="4">
+        <v>45977.729166666664</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="4">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -723,14 +783,17 @@
       <c r="C19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="3">
-        <v>45978</v>
+      <c r="D19" s="4">
+        <v>45978.729166666664</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" s="4">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -740,14 +803,17 @@
       <c r="C20" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="3">
-        <v>45986</v>
+      <c r="D20" s="4">
+        <v>45986.729166666664</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" s="4">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -757,14 +823,17 @@
       <c r="C21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="3">
-        <v>46356</v>
+      <c r="D21" s="4">
+        <v>46356.729166666664</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="4">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -774,14 +843,17 @@
       <c r="C22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D22" s="3">
-        <v>46004</v>
+      <c r="D22" s="4">
+        <v>46004.729166666664</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="4">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -791,14 +863,17 @@
       <c r="C23" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="3">
-        <v>46005</v>
+      <c r="D23" s="4">
+        <v>46005.729166666664</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="4">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -808,14 +883,17 @@
       <c r="C24" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="3">
-        <v>46021</v>
+      <c r="D24" s="4">
+        <v>46021.729166666664</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="4">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -825,14 +903,17 @@
       <c r="C25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="3">
-        <v>46024</v>
+      <c r="D25" s="4">
+        <v>46024.729166666664</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25" s="4">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -842,14 +923,17 @@
       <c r="C26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="3">
-        <v>46026</v>
+      <c r="D26" s="4">
+        <v>46026.729166666664</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26" s="4">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -859,14 +943,17 @@
       <c r="C27" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="3">
-        <v>46030</v>
+      <c r="D27" s="4">
+        <v>46030.729166666664</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27" s="4">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -876,14 +963,17 @@
       <c r="C28" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D28" s="3">
-        <v>46038</v>
+      <c r="D28" s="4">
+        <v>46038.729166666664</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28" s="4">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -893,14 +983,17 @@
       <c r="C29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D29" s="3">
-        <v>46039</v>
+      <c r="D29" s="4">
+        <v>46039.729166666664</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29" s="4">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -910,14 +1003,17 @@
       <c r="C30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="3">
-        <v>46040</v>
+      <c r="D30" s="4">
+        <v>46040.729166666664</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30" s="4">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -927,11 +1023,14 @@
       <c r="C31" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D31" s="3">
-        <v>46041</v>
+      <c r="D31" s="4">
+        <v>46041.729166666664</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>7</v>
+      </c>
+      <c r="F31" s="4">
+        <v>46104</v>
       </c>
     </row>
   </sheetData>

--- a/backend/Dataset/streaks.xlsx
+++ b/backend/Dataset/streaks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofexeteruk-my.sharepoint.com/personal/whm208_exeter_ac_uk/Documents/Year 2/COM2020/Coursework 1/Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="429" documentId="11_F25DC773A252ABDACC104804C11A51C05ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22217A9C-06D9-4946-893C-BB62631266B0}"/>
+  <xr:revisionPtr revIDLastSave="340" documentId="11_F25DC773A252ABDACC104804C11A51C05ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B80DBF4-DD2D-40FB-AD6A-72FB99E37770}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="8">
   <si>
     <t>streakID</t>
   </si>
@@ -50,16 +50,13 @@
   <si>
     <t>NULL</t>
   </si>
-  <si>
-    <t>currentWeekStart</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -113,12 +110,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -403,17 +399,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.5703125" customWidth="1"/>
     <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="26.85546875" customWidth="1"/>
-    <col min="6" max="6" width="30.42578125" customWidth="1"/>
+    <col min="4" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -429,11 +423,8 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -443,17 +434,14 @@
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4">
-        <v>45536.729166666664</v>
-      </c>
-      <c r="E2" s="4">
-        <v>45550.729166666664</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D2" s="3">
+        <v>45536</v>
+      </c>
+      <c r="E2" s="3">
+        <v>45550</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -463,17 +451,14 @@
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="4">
-        <v>45546.729166666664</v>
-      </c>
-      <c r="E3" s="4">
-        <v>45555.729166666664</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D3" s="3">
+        <v>45546</v>
+      </c>
+      <c r="E3" s="3">
+        <v>45555</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -483,17 +468,14 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="4">
-        <v>45556.729166666664</v>
-      </c>
-      <c r="E4" s="4">
-        <v>45590.729166666664</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D4" s="3">
+        <v>45556</v>
+      </c>
+      <c r="E4" s="3">
+        <v>45590</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -503,17 +485,14 @@
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="4">
-        <v>45569.729166666664</v>
-      </c>
-      <c r="E5" s="4">
-        <v>45695.729166666664</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D5" s="3">
+        <v>45569</v>
+      </c>
+      <c r="E5" s="3">
+        <v>45695</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -523,17 +502,14 @@
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="4">
-        <v>45597.729166666664</v>
-      </c>
-      <c r="E6" s="4">
-        <v>45632.729166666664</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D6" s="3">
+        <v>45597</v>
+      </c>
+      <c r="E6" s="3">
+        <v>45632</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -543,17 +519,14 @@
       <c r="C7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="4">
-        <v>45647.729166666664</v>
-      </c>
-      <c r="E7" s="4">
-        <v>46011.729166666664</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D7" s="3">
+        <v>45647</v>
+      </c>
+      <c r="E7" s="3">
+        <v>46011</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -563,17 +536,14 @@
       <c r="C8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="4">
-        <v>45659.729166666664</v>
-      </c>
-      <c r="E8" s="4">
-        <v>45729.729166666664</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D8" s="3">
+        <v>45659</v>
+      </c>
+      <c r="E8" s="3">
+        <v>45729</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -583,17 +553,14 @@
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="4">
-        <v>45702.729166666664</v>
-      </c>
-      <c r="E9" s="4">
-        <v>45716.729166666664</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D9" s="3">
+        <v>45702</v>
+      </c>
+      <c r="E9" s="3">
+        <v>45716</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -603,17 +570,14 @@
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="4">
-        <v>45717.729166666664</v>
-      </c>
-      <c r="E10" s="4">
-        <v>45745.729166666664</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D10" s="3">
+        <v>45717</v>
+      </c>
+      <c r="E10" s="3">
+        <v>45745</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -623,17 +587,14 @@
       <c r="C11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="4">
-        <v>45737.729166666664</v>
-      </c>
-      <c r="E11" s="4">
-        <v>45772.729166666664</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D11" s="3">
+        <v>45737</v>
+      </c>
+      <c r="E11" s="3">
+        <v>45772</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -643,17 +604,14 @@
       <c r="C12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="4">
-        <v>45748.729166666664</v>
-      </c>
-      <c r="E12" s="4">
-        <v>45769.729166666664</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D12" s="3">
+        <v>45748</v>
+      </c>
+      <c r="E12" s="3">
+        <v>45769</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -663,17 +621,14 @@
       <c r="C13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="4">
-        <v>45781.729166666664</v>
-      </c>
-      <c r="E13" s="4">
-        <v>45802.729166666664</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D13" s="3">
+        <v>45781</v>
+      </c>
+      <c r="E13" s="3">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -683,17 +638,14 @@
       <c r="C14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="4">
-        <v>45803.729166666664</v>
-      </c>
-      <c r="E14" s="4">
-        <v>45817.729166666664</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D14" s="3">
+        <v>45803</v>
+      </c>
+      <c r="E14" s="3">
+        <v>45817</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -703,17 +655,14 @@
       <c r="C15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="4">
-        <v>45829.729166666664</v>
-      </c>
-      <c r="E15" s="4">
-        <v>45843.729166666664</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D15" s="3">
+        <v>45829</v>
+      </c>
+      <c r="E15" s="3">
+        <v>45843</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -723,17 +672,14 @@
       <c r="C16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="4">
-        <v>45901.729166666664</v>
-      </c>
-      <c r="E16" s="4">
-        <v>45936.729166666664</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D16" s="3">
+        <v>45901</v>
+      </c>
+      <c r="E16" s="3">
+        <v>45936</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -743,17 +689,14 @@
       <c r="C17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="4">
-        <v>45961.729166666664</v>
+      <c r="D17" s="3">
+        <v>45961</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="4">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -763,17 +706,14 @@
       <c r="C18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="4">
-        <v>45977.729166666664</v>
+      <c r="D18" s="3">
+        <v>45977</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="4">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -783,17 +723,14 @@
       <c r="C19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="4">
-        <v>45978.729166666664</v>
+      <c r="D19" s="3">
+        <v>45978</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="4">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -803,17 +740,14 @@
       <c r="C20" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="4">
-        <v>45986.729166666664</v>
+      <c r="D20" s="3">
+        <v>45986</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="4">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -823,17 +757,14 @@
       <c r="C21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="4">
-        <v>46356.729166666664</v>
+      <c r="D21" s="3">
+        <v>46356</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F21" s="4">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -843,17 +774,14 @@
       <c r="C22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D22" s="4">
-        <v>46004.729166666664</v>
+      <c r="D22" s="3">
+        <v>46004</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F22" s="4">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -863,17 +791,14 @@
       <c r="C23" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="4">
-        <v>46005.729166666664</v>
+      <c r="D23" s="3">
+        <v>46005</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F23" s="4">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -883,17 +808,14 @@
       <c r="C24" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="4">
-        <v>46021.729166666664</v>
+      <c r="D24" s="3">
+        <v>46021</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F24" s="4">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -903,17 +825,14 @@
       <c r="C25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="4">
-        <v>46024.729166666664</v>
+      <c r="D25" s="3">
+        <v>46024</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="4">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -923,17 +842,14 @@
       <c r="C26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="4">
-        <v>46026.729166666664</v>
+      <c r="D26" s="3">
+        <v>46026</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F26" s="4">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -943,17 +859,14 @@
       <c r="C27" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="4">
-        <v>46030.729166666664</v>
+      <c r="D27" s="3">
+        <v>46030</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F27" s="4">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -963,17 +876,14 @@
       <c r="C28" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D28" s="4">
-        <v>46038.729166666664</v>
+      <c r="D28" s="3">
+        <v>46038</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F28" s="4">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -983,17 +893,14 @@
       <c r="C29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D29" s="4">
-        <v>46039.729166666664</v>
+      <c r="D29" s="3">
+        <v>46039</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F29" s="4">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1003,17 +910,14 @@
       <c r="C30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="4">
-        <v>46040.729166666664</v>
+      <c r="D30" s="3">
+        <v>46040</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F30" s="4">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1023,14 +927,11 @@
       <c r="C31" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D31" s="4">
-        <v>46041.729166666664</v>
+      <c r="D31" s="3">
+        <v>46041</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="F31" s="4">
-        <v>46104</v>
       </c>
     </row>
   </sheetData>
